--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Qwen3-Next-80B-A3B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Qwen3-Next-80B-A3B-Instruct/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,13 +450,13 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
         <v>0</v>
